--- a/backend/data/financials_by_company/000560.SZ.xlsx
+++ b/backend/data/financials_by_company/000560.SZ.xlsx
@@ -692,658 +692,658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>297740129.13</v>
+        <v>198214179.3625</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>5278781333.64</v>
+        <v>2696272364.98</v>
       </c>
       <c r="E2" t="n">
-        <v>1190960516.52</v>
+        <v>792856717.45</v>
       </c>
       <c r="F2" t="n">
-        <v>1190960516.52</v>
+        <v>792856717.45</v>
       </c>
       <c r="G2" t="n">
-        <v>73412261.43000001</v>
+        <v>165960237.25</v>
       </c>
       <c r="H2" t="n">
-        <v>5517724035.36</v>
+        <v>2683819201.44</v>
       </c>
       <c r="I2" t="n">
-        <v>11310764105.38</v>
+        <v>9783808309.360001</v>
       </c>
       <c r="J2" t="n">
-        <v>6469741850.16</v>
+        <v>3489129082.43</v>
       </c>
       <c r="K2" t="n">
-        <v>952017814.8</v>
+        <v>805309880.99</v>
       </c>
       <c r="L2" t="n">
-        <v>-631276648.73</v>
+        <v>-482181486.82</v>
       </c>
       <c r="M2" t="n">
-        <v>826808068.3099999</v>
+        <v>573973509.78</v>
       </c>
       <c r="N2" t="n">
-        <v>236483326.44</v>
+        <v>172495417.63</v>
       </c>
       <c r="O2" t="n">
-        <v>-819808125.96</v>
+        <v>-428682300.8375</v>
       </c>
       <c r="P2" t="n">
-        <v>73412261.43000001</v>
+        <v>165960237.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>13026841600.86</v>
+        <v>12085650307.34</v>
       </c>
       <c r="R2" t="n">
-        <v>6003779.36</v>
+        <v>25158798.75</v>
       </c>
       <c r="S2" t="n">
-        <v>140601777.43</v>
+        <v>218215908.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2352957097</v>
+        <v>2334180552</v>
       </c>
       <c r="U2" t="n">
-        <v>2352957097</v>
+        <v>2334180552</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0312</v>
+        <v>0.0711</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0312</v>
+        <v>0.0711</v>
       </c>
       <c r="X2" t="n">
-        <v>73412261.43000001</v>
+        <v>165960237.25</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>73412261.43000001</v>
+        <v>165960237.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>3379096.35</v>
+        <v>35179258.31</v>
       </c>
       <c r="AB2" t="n">
-        <v>70033165.08</v>
+        <v>130780978.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>70033165.08</v>
+        <v>130780978.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>55176581.41</v>
+        <v>100555392.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>125209746.49</v>
+        <v>231336371.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>-15392030.94</v>
+        <v>26234312.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>1198192288.68</v>
+        <v>760212616.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1310850721.34</v>
+        <v>-922085613.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>114011649.44</v>
+        <v>162641681.66</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1353216.78</v>
+        <v>-768684.92</v>
       </c>
       <c r="AK2" t="n">
-        <v>-631276648.73</v>
+        <v>-482181486.82</v>
       </c>
       <c r="AL2" t="n">
-        <v>40951906.86</v>
+        <v>80703394.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>826808068.3099999</v>
+        <v>573973509.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>236483326.44</v>
+        <v>172495417.63</v>
       </c>
       <c r="AO2" t="n">
-        <v>-490747135.21</v>
+        <v>-122776488.59</v>
       </c>
       <c r="AP2" t="n">
-        <v>1716077495.48</v>
+        <v>2301841997.98</v>
       </c>
       <c r="AQ2" t="n">
-        <v>58570356.32</v>
+        <v>101440715.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>105334906.36</v>
+        <v>183455594.46</v>
       </c>
       <c r="AS2" t="n">
-        <v>105334906.36</v>
+        <v>183455594.46</v>
       </c>
       <c r="AT2" t="n">
-        <v>95059225.81</v>
+        <v>31317872.59</v>
       </c>
       <c r="AU2" t="n">
-        <v>466117279.59</v>
+        <v>888356880.61</v>
       </c>
       <c r="AV2" t="n">
-        <v>220425730.95</v>
+        <v>353931140.36</v>
       </c>
       <c r="AW2" t="n">
-        <v>245691548.64</v>
+        <v>534425740.25</v>
       </c>
       <c r="AX2" t="n">
-        <v>6003779.36</v>
+        <v>25158798.75</v>
       </c>
       <c r="AY2" t="n">
-        <v>1225330360.27</v>
+        <v>2179065509.39</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11310764105.38</v>
+        <v>9783808309.360001</v>
       </c>
       <c r="BA2" t="n">
-        <v>12536094465.65</v>
+        <v>11962873818.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>12536094465.65</v>
+        <v>11962873818.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>4961728.82032</v>
+        <v>194413037.48</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007107</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>4429782696.42</v>
+        <v>4637539146.21</v>
       </c>
       <c r="E3" t="n">
-        <v>698136103.8200001</v>
+        <v>777652149.92</v>
       </c>
       <c r="F3" t="n">
-        <v>698136103.8200001</v>
+        <v>777652149.92</v>
       </c>
       <c r="G3" t="n">
-        <v>-848292259.15</v>
+        <v>-309694834.25</v>
       </c>
       <c r="H3" t="n">
-        <v>5124084997.68</v>
+        <v>4854159997.55</v>
       </c>
       <c r="I3" t="n">
-        <v>10947070275.13</v>
+        <v>10662117516.38</v>
       </c>
       <c r="J3" t="n">
-        <v>5127918800.24</v>
+        <v>5415191296.13</v>
       </c>
       <c r="K3" t="n">
-        <v>3833802.56</v>
+        <v>561031298.58</v>
       </c>
       <c r="L3" t="n">
-        <v>-655405179.83</v>
+        <v>-682838351.8099999</v>
       </c>
       <c r="M3" t="n">
-        <v>859882041.65</v>
+        <v>840438721.36</v>
       </c>
       <c r="N3" t="n">
-        <v>248170124.28</v>
+        <v>207050475.28</v>
       </c>
       <c r="O3" t="n">
-        <v>-1541466634.14968</v>
+        <v>-892933946.6900001</v>
       </c>
       <c r="P3" t="n">
-        <v>-848292259.15</v>
+        <v>-309694834.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>12965335122.37</v>
+        <v>12078526636.93</v>
       </c>
       <c r="R3" t="n">
-        <v>21287360.98</v>
+        <v>28468318.23</v>
       </c>
       <c r="S3" t="n">
-        <v>-846330827.84</v>
+        <v>-287246897</v>
       </c>
       <c r="T3" t="n">
-        <v>2355713022</v>
+        <v>2355093797</v>
       </c>
       <c r="U3" t="n">
-        <v>2355713022</v>
+        <v>2355093797</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3601</v>
+        <v>-0.1315</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3601</v>
+        <v>-0.1315</v>
       </c>
       <c r="X3" t="n">
-        <v>-848292259.15</v>
+        <v>-309694834.25</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-848292259.15</v>
+        <v>-309694834.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1671952.49</v>
+        <v>25830929.96</v>
       </c>
       <c r="AB3" t="n">
-        <v>-849964211.64</v>
+        <v>-335525764.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>-849964211.64</v>
+        <v>-335525764.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>-6084027.45</v>
+        <v>56118341.43</v>
       </c>
       <c r="AE3" t="n">
-        <v>-856048239.09</v>
+        <v>-279407422.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>-9717411.25</v>
+        <v>7839474.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>726256657.9400001</v>
+        <v>785653491.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1207270795.47</v>
+        <v>-1090022771.21</v>
       </c>
       <c r="AI3" t="n">
-        <v>162591690.94</v>
+        <v>304130563.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>318422446.59</v>
+        <v>238716.53</v>
       </c>
       <c r="AK3" t="n">
-        <v>-655405179.83</v>
+        <v>-682838351.8099999</v>
       </c>
       <c r="AL3" t="n">
-        <v>43693262.46</v>
+        <v>49450105.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>859882041.65</v>
+        <v>840438721.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>248170124.28</v>
+        <v>207050475.28</v>
       </c>
       <c r="AO3" t="n">
-        <v>-873602290.76</v>
+        <v>-405116478.53</v>
       </c>
       <c r="AP3" t="n">
-        <v>2018264847.24</v>
+        <v>1416409120.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>60628443.65</v>
+        <v>65821009.69</v>
       </c>
       <c r="AR3" t="n">
-        <v>111554371.45</v>
+        <v>135514861.19</v>
       </c>
       <c r="AS3" t="n">
-        <v>111554371.45</v>
+        <v>135514861.19</v>
       </c>
       <c r="AT3" t="n">
-        <v>40095921.71</v>
+        <v>36982852.64</v>
       </c>
       <c r="AU3" t="n">
-        <v>647171036.89</v>
+        <v>520914871.82</v>
       </c>
       <c r="AV3" t="n">
-        <v>364465562.88</v>
+        <v>261221078.61</v>
       </c>
       <c r="AW3" t="n">
-        <v>282705474.01</v>
+        <v>259693793.21</v>
       </c>
       <c r="AX3" t="n">
-        <v>21287360.98</v>
+        <v>28468318.23</v>
       </c>
       <c r="AY3" t="n">
-        <v>1144662556.48</v>
+        <v>1011292642.02</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10947070275.13</v>
+        <v>10662117516.38</v>
       </c>
       <c r="BA3" t="n">
-        <v>12091732831.61</v>
+        <v>11673410158.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>12091732831.61</v>
+        <v>11673410158.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>194413037.48</v>
+        <v>4961728.82032</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.007107</v>
       </c>
       <c r="D4" t="n">
-        <v>4637539146.21</v>
+        <v>4429782696.42</v>
       </c>
       <c r="E4" t="n">
-        <v>777652149.92</v>
+        <v>698136103.8200001</v>
       </c>
       <c r="F4" t="n">
-        <v>777652149.92</v>
+        <v>698136103.8200001</v>
       </c>
       <c r="G4" t="n">
-        <v>-309694834.25</v>
+        <v>-848292259.15</v>
       </c>
       <c r="H4" t="n">
-        <v>4854159997.55</v>
+        <v>5124084997.68</v>
       </c>
       <c r="I4" t="n">
-        <v>10662117516.38</v>
+        <v>10947070275.13</v>
       </c>
       <c r="J4" t="n">
-        <v>5415191296.13</v>
+        <v>5127918800.24</v>
       </c>
       <c r="K4" t="n">
-        <v>561031298.58</v>
+        <v>3833802.56</v>
       </c>
       <c r="L4" t="n">
-        <v>-682838351.8099999</v>
+        <v>-655405179.83</v>
       </c>
       <c r="M4" t="n">
-        <v>840438721.36</v>
+        <v>859882041.65</v>
       </c>
       <c r="N4" t="n">
-        <v>207050475.28</v>
+        <v>248170124.28</v>
       </c>
       <c r="O4" t="n">
-        <v>-892933946.6900001</v>
+        <v>-1541466634.14968</v>
       </c>
       <c r="P4" t="n">
-        <v>-309694834.25</v>
+        <v>-848292259.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>12078526636.93</v>
+        <v>12965335122.37</v>
       </c>
       <c r="R4" t="n">
-        <v>28468318.23</v>
+        <v>21287360.98</v>
       </c>
       <c r="S4" t="n">
-        <v>-287246897</v>
+        <v>-846330827.84</v>
       </c>
       <c r="T4" t="n">
-        <v>2355093797</v>
+        <v>2355713022</v>
       </c>
       <c r="U4" t="n">
-        <v>2355093797</v>
+        <v>2355713022</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1315</v>
+        <v>-0.3601</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1315</v>
+        <v>-0.3601</v>
       </c>
       <c r="X4" t="n">
-        <v>-309694834.25</v>
+        <v>-848292259.15</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-309694834.25</v>
+        <v>-848292259.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>25830929.96</v>
+        <v>1671952.49</v>
       </c>
       <c r="AB4" t="n">
-        <v>-335525764.21</v>
+        <v>-849964211.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>-335525764.21</v>
+        <v>-849964211.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>56118341.43</v>
+        <v>-6084027.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>-279407422.78</v>
+        <v>-856048239.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>7839474.22</v>
+        <v>-9717411.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>785653491.23</v>
+        <v>726256657.9400001</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1090022771.21</v>
+        <v>-1207270795.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>304130563.45</v>
+        <v>162591690.94</v>
       </c>
       <c r="AJ4" t="n">
-        <v>238716.53</v>
+        <v>318422446.59</v>
       </c>
       <c r="AK4" t="n">
-        <v>-682838351.8099999</v>
+        <v>-655405179.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>49450105.73</v>
+        <v>43693262.46</v>
       </c>
       <c r="AM4" t="n">
-        <v>840438721.36</v>
+        <v>859882041.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>207050475.28</v>
+        <v>248170124.28</v>
       </c>
       <c r="AO4" t="n">
-        <v>-405116478.53</v>
+        <v>-873602290.76</v>
       </c>
       <c r="AP4" t="n">
-        <v>1416409120.55</v>
+        <v>2018264847.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>65821009.69</v>
+        <v>60628443.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>135514861.19</v>
+        <v>111554371.45</v>
       </c>
       <c r="AS4" t="n">
-        <v>135514861.19</v>
+        <v>111554371.45</v>
       </c>
       <c r="AT4" t="n">
-        <v>36982852.64</v>
+        <v>40095921.71</v>
       </c>
       <c r="AU4" t="n">
-        <v>520914871.82</v>
+        <v>647171036.89</v>
       </c>
       <c r="AV4" t="n">
-        <v>261221078.61</v>
+        <v>364465562.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>259693793.21</v>
+        <v>282705474.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>28468318.23</v>
+        <v>21287360.98</v>
       </c>
       <c r="AY4" t="n">
-        <v>1011292642.02</v>
+        <v>1144662556.48</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10662117516.38</v>
+        <v>10947070275.13</v>
       </c>
       <c r="BA4" t="n">
-        <v>11673410158.4</v>
+        <v>12091732831.61</v>
       </c>
       <c r="BB4" t="n">
-        <v>11673410158.4</v>
+        <v>12091732831.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>198214179.3625</v>
+        <v>297740129.13</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>2696272364.98</v>
+        <v>5278781333.64</v>
       </c>
       <c r="E5" t="n">
-        <v>792856717.45</v>
+        <v>1190960516.52</v>
       </c>
       <c r="F5" t="n">
-        <v>792856717.45</v>
+        <v>1190960516.52</v>
       </c>
       <c r="G5" t="n">
-        <v>165960237.25</v>
+        <v>73412261.43000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2683819201.44</v>
+        <v>5517724035.36</v>
       </c>
       <c r="I5" t="n">
-        <v>9783808309.360001</v>
+        <v>11310764105.38</v>
       </c>
       <c r="J5" t="n">
-        <v>3489129082.43</v>
+        <v>6469741850.16</v>
       </c>
       <c r="K5" t="n">
-        <v>805309880.99</v>
+        <v>952017814.8</v>
       </c>
       <c r="L5" t="n">
-        <v>-482181486.82</v>
+        <v>-631276648.73</v>
       </c>
       <c r="M5" t="n">
-        <v>573973509.78</v>
+        <v>826808068.3099999</v>
       </c>
       <c r="N5" t="n">
-        <v>172495417.63</v>
+        <v>236483326.44</v>
       </c>
       <c r="O5" t="n">
-        <v>-428682300.8375</v>
+        <v>-819808125.96</v>
       </c>
       <c r="P5" t="n">
-        <v>165960237.25</v>
+        <v>73412261.43000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>12085650307.34</v>
+        <v>13026841600.86</v>
       </c>
       <c r="R5" t="n">
-        <v>25158798.75</v>
+        <v>6003779.36</v>
       </c>
       <c r="S5" t="n">
-        <v>218215908.88</v>
+        <v>140601777.43</v>
       </c>
       <c r="T5" t="n">
-        <v>2334180552</v>
+        <v>2352957097</v>
       </c>
       <c r="U5" t="n">
-        <v>2334180552</v>
+        <v>2352957097</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0711</v>
+        <v>0.0312</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0711</v>
+        <v>0.0312</v>
       </c>
       <c r="X5" t="n">
-        <v>165960237.25</v>
+        <v>73412261.43000001</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>165960237.25</v>
+        <v>73412261.43000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>35179258.31</v>
+        <v>3379096.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>130780978.94</v>
+        <v>70033165.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>130780978.94</v>
+        <v>70033165.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>100555392.27</v>
+        <v>55176581.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>231336371.21</v>
+        <v>125209746.49</v>
       </c>
       <c r="AF5" t="n">
-        <v>26234312.33</v>
+        <v>-15392030.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>760212616.55</v>
+        <v>1198192288.68</v>
       </c>
       <c r="AH5" t="n">
-        <v>-922085613.29</v>
+        <v>-1310850721.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>162641681.66</v>
+        <v>114011649.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-768684.92</v>
+        <v>-1353216.78</v>
       </c>
       <c r="AK5" t="n">
-        <v>-482181486.82</v>
+        <v>-631276648.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>80703394.67</v>
+        <v>40951906.86</v>
       </c>
       <c r="AM5" t="n">
-        <v>573973509.78</v>
+        <v>826808068.3099999</v>
       </c>
       <c r="AN5" t="n">
-        <v>172495417.63</v>
+        <v>236483326.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>-122776488.59</v>
+        <v>-490747135.21</v>
       </c>
       <c r="AP5" t="n">
-        <v>2301841997.98</v>
+        <v>1716077495.48</v>
       </c>
       <c r="AQ5" t="n">
-        <v>101440715.19</v>
+        <v>58570356.32</v>
       </c>
       <c r="AR5" t="n">
-        <v>183455594.46</v>
+        <v>105334906.36</v>
       </c>
       <c r="AS5" t="n">
-        <v>183455594.46</v>
+        <v>105334906.36</v>
       </c>
       <c r="AT5" t="n">
-        <v>31317872.59</v>
+        <v>95059225.81</v>
       </c>
       <c r="AU5" t="n">
-        <v>888356880.61</v>
+        <v>466117279.59</v>
       </c>
       <c r="AV5" t="n">
-        <v>353931140.36</v>
+        <v>220425730.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>534425740.25</v>
+        <v>245691548.64</v>
       </c>
       <c r="AX5" t="n">
-        <v>25158798.75</v>
+        <v>6003779.36</v>
       </c>
       <c r="AY5" t="n">
-        <v>2179065509.39</v>
+        <v>1225330360.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9783808309.360001</v>
+        <v>11310764105.38</v>
       </c>
       <c r="BA5" t="n">
-        <v>11962873818.75</v>
+        <v>12536094465.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>11962873818.75</v>
+        <v>12536094465.65</v>
       </c>
     </row>
   </sheetData>
@@ -1739,91 +1739,219 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2355500851</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2355500851</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15399967833.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4192749586.38</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13373523792.98</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-2611946922.69</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4192749586.38</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5426253095.02</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10569590116.54</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11018790868.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10710919504.56</v>
+      </c>
+      <c r="M2" t="n">
+        <v>141329388.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10569590116.54</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>2371505873.14</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5335629485.23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2355500851</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2355500851</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>22252591902.17</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6762198832.58</v>
+      </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>3577943.62</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>187597950.76</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>695569091.02</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5875453847.18</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5426253095.02</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>449200752.16</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15490393069.59</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>623942142.05</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9524513986.57</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2354732924.28</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4595932257.06</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2912660173.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2659739.07</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1126110457.37</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>554501887.12</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>32963511406.73</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20085065259.83</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>288413.2</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>871249471.0599999</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>569878239.8099999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>43377778</v>
+      </c>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>43377778</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>93797530.12</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3042395128.87</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6376840530.16</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1565294816.55</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4811545713.61</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9053656801.120001</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-541310602.4400001</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9594967403.559999</v>
+      </c>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>9105736386.049999</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>32431448.06</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>456799569.45</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12878446146.9</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3410206611.53</v>
+      </c>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="n">
-        <v>-619189035.85</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>908410682.98</v>
-      </c>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
+      <c r="BK2" t="n">
+        <v>1361141778.37</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>620331878.28</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>568648625.54</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>51683252.74</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1517342835.23</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1204635397.81</v>
+      </c>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="n">
+        <v>4764787645.68</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>516241843.81</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>4248545801.87</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>626674953.49</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>3621870848.38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>2355500851</v>
@@ -1832,46 +1960,44 @@
         <v>2355500851</v>
       </c>
       <c r="D3" t="n">
-        <v>15563612228.59</v>
+        <v>16666527214.05</v>
       </c>
       <c r="E3" t="n">
-        <v>3580050671.28</v>
+        <v>4252030742.66</v>
       </c>
       <c r="F3" t="n">
-        <v>11429443289.47</v>
+        <v>12792722870.26</v>
       </c>
       <c r="G3" t="n">
-        <v>-4405424775.96</v>
+        <v>-3732458567.85</v>
       </c>
       <c r="H3" t="n">
-        <v>3580050671.28</v>
+        <v>4252030742.66</v>
       </c>
       <c r="I3" t="n">
-        <v>4159661626.59</v>
+        <v>4620932626.61</v>
       </c>
       <c r="J3" t="n">
-        <v>9385985309.629999</v>
+        <v>10291615903.81</v>
       </c>
       <c r="K3" t="n">
-        <v>10252422540.32</v>
+        <v>10894488214.5</v>
       </c>
       <c r="L3" t="n">
-        <v>9443197398.040001</v>
+        <v>10390593009.16</v>
       </c>
       <c r="M3" t="n">
-        <v>57212088.41</v>
+        <v>98977105.34999999</v>
       </c>
       <c r="N3" t="n">
-        <v>9385985309.629999</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>10291615903.81</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1265448204.55</v>
+        <v>2042992576.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5296157506.42</v>
+        <v>5340055272.91</v>
       </c>
       <c r="R3" t="n">
         <v>2355500851</v>
@@ -1879,174 +2005,164 @@
       <c r="S3" t="n">
         <v>2355500851</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>20793387903.13</v>
+        <v>22149891399</v>
       </c>
       <c r="V3" t="n">
-        <v>5687342952.72</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
+        <v>5847984025.06</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>502014.39</v>
+        <v>500846.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>22363869</v>
       </c>
       <c r="Z3" t="n">
-        <v>660742081.05</v>
+        <v>601314372.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>5026098857.28</v>
+        <v>5223804937.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>4159661626.59</v>
+        <v>4620932626.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>866437230.6900001</v>
+        <v>602872310.6900001</v>
       </c>
       <c r="AD3" t="n">
-        <v>15106044950.41</v>
+        <v>16301907373.94</v>
       </c>
       <c r="AE3" t="n">
-        <v>671089292.04</v>
+        <v>626832616.37</v>
       </c>
       <c r="AF3" t="n">
-        <v>10537513371.31</v>
+        <v>11442722276.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1177020749.15</v>
+        <v>1898234655.76</v>
       </c>
       <c r="AH3" t="n">
-        <v>3388633566.1</v>
+        <v>3528175128.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>2369131622.8</v>
+        <v>1951956310.46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>218184.07</v>
+        <v>651574.0699999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>626805013.77</v>
+        <v>1112042754.62</v>
       </c>
       <c r="AL3" t="n">
-        <v>392478745.46</v>
+        <v>463524489.07</v>
       </c>
       <c r="AM3" t="n">
-        <v>30236585301.17</v>
+        <v>32540484408.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>19535965126.72</v>
+        <v>19971035602.07</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>475954682.09</v>
+        <v>640014908.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>593163506.5700001</v>
+        <v>573704241.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>159851798.52</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
+        <v>21969300</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>159851798.52</v>
+        <v>21969300</v>
       </c>
       <c r="AU3" t="n">
-        <v>97303351.09</v>
+        <v>90574535.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>2865227504</v>
+        <v>3123691172.87</v>
       </c>
       <c r="AW3" t="n">
-        <v>5805934638.35</v>
+        <v>6039585161.15</v>
       </c>
       <c r="AX3" t="n">
-        <v>1345228104.03</v>
+        <v>1228039447.54</v>
       </c>
       <c r="AY3" t="n">
-        <v>4460706534.32</v>
+        <v>4811545713.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9533126854.059999</v>
+        <v>9371537579.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>-395262132.14</v>
+        <v>-549058244.41</v>
       </c>
       <c r="BB3" t="n">
-        <v>9928388986.200001</v>
+        <v>9920595823.75</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>943830.1899999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>9037366336.620001</v>
+        <v>9441232840.690001</v>
       </c>
       <c r="BE3" t="n">
-        <v>14811064.2</v>
+        <v>21891875.77</v>
       </c>
       <c r="BF3" t="n">
-        <v>876211585.38</v>
+        <v>456527277.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>10700620174.45</v>
+        <v>12569448806.09</v>
       </c>
       <c r="BH3" t="n">
-        <v>4211480613.58</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
+        <v>4021005739.02</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>1095462791.98</v>
+        <v>1497429472.89</v>
       </c>
       <c r="BL3" t="n">
-        <v>216542142.32</v>
+        <v>509407926.74</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>183705673.24</v>
+        <v>464569025.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>32836469.08</v>
+        <v>44838901.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>1118225617.9</v>
+        <v>1431950849.01</v>
       </c>
       <c r="BQ3" t="n">
-        <v>504264323.53</v>
+        <v>898714798.77</v>
       </c>
       <c r="BR3" t="n">
-        <v>-592970655.91</v>
+        <v>-418016951.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>1097234979.44</v>
+        <v>1316731750.07</v>
       </c>
       <c r="BT3" t="n">
-        <v>3554644685.14</v>
+        <v>4210940019.66</v>
       </c>
       <c r="BU3" t="n">
-        <v>316815184.5</v>
+        <v>429334737.89</v>
       </c>
       <c r="BV3" t="n">
-        <v>3237829500.64</v>
+        <v>3781605281.77</v>
       </c>
       <c r="BW3" t="n">
-        <v>340769651.42</v>
+        <v>372307961.72</v>
       </c>
       <c r="BX3" t="n">
-        <v>2897059849.22</v>
+        <v>3409297320.05</v>
       </c>
     </row>
     <row r="4">
@@ -2279,7 +2395,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>2355500851</v>
@@ -2288,44 +2404,46 @@
         <v>2355500851</v>
       </c>
       <c r="D5" t="n">
-        <v>16666527214.05</v>
+        <v>15563612228.59</v>
       </c>
       <c r="E5" t="n">
-        <v>4252030742.66</v>
+        <v>3580050671.28</v>
       </c>
       <c r="F5" t="n">
-        <v>12792722870.26</v>
+        <v>11429443289.47</v>
       </c>
       <c r="G5" t="n">
-        <v>-3732458567.85</v>
+        <v>-4405424775.96</v>
       </c>
       <c r="H5" t="n">
-        <v>4252030742.66</v>
+        <v>3580050671.28</v>
       </c>
       <c r="I5" t="n">
-        <v>4620932626.61</v>
+        <v>4159661626.59</v>
       </c>
       <c r="J5" t="n">
-        <v>10291615903.81</v>
+        <v>9385985309.629999</v>
       </c>
       <c r="K5" t="n">
-        <v>10894488214.5</v>
+        <v>10252422540.32</v>
       </c>
       <c r="L5" t="n">
-        <v>10390593009.16</v>
+        <v>9443197398.040001</v>
       </c>
       <c r="M5" t="n">
-        <v>98977105.34999999</v>
+        <v>57212088.41</v>
       </c>
       <c r="N5" t="n">
-        <v>10291615903.81</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>9385985309.629999</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>2042992576.08</v>
+        <v>1265448204.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>5340055272.91</v>
+        <v>5296157506.42</v>
       </c>
       <c r="R5" t="n">
         <v>2355500851</v>
@@ -2333,377 +2451,259 @@
       <c r="S5" t="n">
         <v>2355500851</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
       <c r="U5" t="n">
-        <v>22149891399</v>
+        <v>20793387903.13</v>
       </c>
       <c r="V5" t="n">
-        <v>5847984025.06</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>5687342952.72</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" t="n">
-        <v>500846.31</v>
+        <v>502014.39</v>
       </c>
       <c r="Y5" t="n">
-        <v>22363869</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>601314372.45</v>
+        <v>660742081.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>5223804937.3</v>
+        <v>5026098857.28</v>
       </c>
       <c r="AB5" t="n">
-        <v>4620932626.61</v>
+        <v>4159661626.59</v>
       </c>
       <c r="AC5" t="n">
-        <v>602872310.6900001</v>
+        <v>866437230.6900001</v>
       </c>
       <c r="AD5" t="n">
-        <v>16301907373.94</v>
+        <v>15106044950.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>626832616.37</v>
+        <v>671089292.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>11442722276.75</v>
+        <v>10537513371.31</v>
       </c>
       <c r="AG5" t="n">
-        <v>1898234655.76</v>
+        <v>1177020749.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>3528175128.22</v>
+        <v>3388633566.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>1951956310.46</v>
+        <v>2369131622.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>651574.0699999999</v>
+        <v>218184.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>1112042754.62</v>
+        <v>626805013.77</v>
       </c>
       <c r="AL5" t="n">
-        <v>463524489.07</v>
+        <v>392478745.46</v>
       </c>
       <c r="AM5" t="n">
-        <v>32540484408.16</v>
+        <v>30236585301.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>19971035602.07</v>
+        <v>19535965126.72</v>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>640014908.4</v>
+        <v>475954682.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>573704241.09</v>
+        <v>593163506.5700001</v>
       </c>
       <c r="AR5" t="n">
-        <v>21969300</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>159851798.52</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
       <c r="AT5" t="n">
-        <v>21969300</v>
+        <v>159851798.52</v>
       </c>
       <c r="AU5" t="n">
-        <v>90574535.45</v>
+        <v>97303351.09</v>
       </c>
       <c r="AV5" t="n">
-        <v>3123691172.87</v>
+        <v>2865227504</v>
       </c>
       <c r="AW5" t="n">
-        <v>6039585161.15</v>
+        <v>5805934638.35</v>
       </c>
       <c r="AX5" t="n">
-        <v>1228039447.54</v>
+        <v>1345228104.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>4811545713.61</v>
+        <v>4460706534.32</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9371537579.34</v>
+        <v>9533126854.059999</v>
       </c>
       <c r="BA5" t="n">
-        <v>-549058244.41</v>
+        <v>-395262132.14</v>
       </c>
       <c r="BB5" t="n">
-        <v>9920595823.75</v>
+        <v>9928388986.200001</v>
       </c>
       <c r="BC5" t="n">
-        <v>943830.1899999999</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>9441232840.690001</v>
+        <v>9037366336.620001</v>
       </c>
       <c r="BE5" t="n">
-        <v>21891875.77</v>
+        <v>14811064.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>456527277.1</v>
+        <v>876211585.38</v>
       </c>
       <c r="BG5" t="n">
-        <v>12569448806.09</v>
+        <v>10700620174.45</v>
       </c>
       <c r="BH5" t="n">
-        <v>4021005739.02</v>
-      </c>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
+        <v>4211480613.58</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
       <c r="BK5" t="n">
-        <v>1497429472.89</v>
+        <v>1095462791.98</v>
       </c>
       <c r="BL5" t="n">
-        <v>509407926.74</v>
+        <v>216542142.32</v>
       </c>
       <c r="BM5" t="n">
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>464569025.57</v>
+        <v>183705673.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>44838901.17</v>
+        <v>32836469.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>1431950849.01</v>
+        <v>1118225617.9</v>
       </c>
       <c r="BQ5" t="n">
-        <v>898714798.77</v>
+        <v>504264323.53</v>
       </c>
       <c r="BR5" t="n">
-        <v>-418016951.3</v>
+        <v>-592970655.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>1316731750.07</v>
+        <v>1097234979.44</v>
       </c>
       <c r="BT5" t="n">
-        <v>4210940019.66</v>
+        <v>3554644685.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>429334737.89</v>
+        <v>316815184.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>3781605281.77</v>
+        <v>3237829500.64</v>
       </c>
       <c r="BW5" t="n">
-        <v>372307961.72</v>
+        <v>340769651.42</v>
       </c>
       <c r="BX5" t="n">
-        <v>3409297320.05</v>
+        <v>2897059849.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2355500851</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2355500851</v>
-      </c>
-      <c r="D6" t="n">
-        <v>15399967833.75</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4192749586.38</v>
-      </c>
-      <c r="F6" t="n">
-        <v>13373523792.98</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-2611946922.69</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4192749586.38</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5426253095.02</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10569590116.54</v>
-      </c>
-      <c r="K6" t="n">
-        <v>11018790868.7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>10710919504.56</v>
-      </c>
-      <c r="M6" t="n">
-        <v>141329388.02</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10569590116.54</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>2371505873.14</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5335629485.23</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2355500851</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2355500851</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>22252591902.17</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6762198832.58</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>3577943.62</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>187597950.76</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>695569091.02</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5875453847.18</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5426253095.02</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>449200752.16</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15490393069.59</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>623942142.05</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9524513986.57</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2354732924.28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>4595932257.06</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2912660173.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2659739.07</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1126110457.37</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>554501887.12</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>32963511406.73</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>20085065259.83</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>288413.2</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>871249471.0599999</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>569878239.8099999</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>43377778</v>
-      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>43377778</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>93797530.12</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3042395128.87</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6376840530.16</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1565294816.55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4811545713.61</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>9053656801.120001</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-541310602.4400001</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9594967403.559999</v>
-      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>9105736386.049999</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>32431448.06</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>456799569.45</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>12878446146.9</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3410206611.53</v>
-      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>1361141778.37</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>620331878.28</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>568648625.54</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>51683252.74</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1517342835.23</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1204635397.81</v>
-      </c>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="n">
-        <v>4764787645.68</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>516241843.81</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>4248545801.87</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>626674953.49</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>3621870848.38</v>
-      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>-619189035.85</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>908410682.98</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2953,564 +2953,564 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>4099379863.63</v>
+        <v>1299076970.68</v>
       </c>
       <c r="C2" t="n">
-        <v>-1991848866.89</v>
+        <v>-2885498675.68</v>
       </c>
       <c r="D2" t="n">
-        <v>1716075709.62</v>
+        <v>3124976372.33</v>
       </c>
       <c r="E2" t="n">
-        <v>-386164707.34</v>
+        <v>-832543322.5700001</v>
       </c>
       <c r="F2" t="n">
-        <v>2900006155.94</v>
+        <v>3621870848.38</v>
       </c>
       <c r="G2" t="n">
-        <v>3274586769.68</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>3766128713.76</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-266417.55</v>
+      </c>
       <c r="I2" t="n">
-        <v>-374580613.74</v>
+        <v>-143991447.83</v>
       </c>
       <c r="J2" t="n">
-        <v>-13682324675.41</v>
+        <v>-4631513518.2</v>
       </c>
       <c r="K2" t="n">
-        <v>-13281215338.76</v>
+        <v>-4632691858.56</v>
       </c>
       <c r="L2" t="n">
-        <v>-118476179.38</v>
+        <v>-224854653.72</v>
       </c>
       <c r="M2" t="n">
-        <v>-275773157.27</v>
+        <v>239477696.65</v>
       </c>
       <c r="N2" t="n">
-        <v>-275773157.27</v>
+        <v>239477696.65</v>
       </c>
       <c r="O2" t="n">
-        <v>-1991848866.89</v>
+        <v>-2885498675.68</v>
       </c>
       <c r="P2" t="n">
-        <v>1716075709.62</v>
+        <v>3124976372.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>8822199490.700001</v>
+        <v>2355901777.12</v>
       </c>
       <c r="R2" t="n">
-        <v>14021037.09</v>
+        <v>-284597915.56</v>
       </c>
       <c r="S2" t="n">
-        <v>1045021037.09</v>
+        <v>4877467888.84</v>
       </c>
       <c r="T2" t="n">
-        <v>-1031000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>169906567.9</v>
-      </c>
-      <c r="V2" t="n">
-        <v>169906567.9</v>
-      </c>
+        <v>-5162065804.4</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>8638271885.709999</v>
+        <v>2640499692.68</v>
       </c>
       <c r="X2" t="n">
-        <v>9024436593.049999</v>
+        <v>3473043015.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>-386164707.34</v>
+        <v>-832543322.5700001</v>
       </c>
       <c r="Z2" t="n">
-        <v>4485544570.97</v>
+        <v>2131620293.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1004136487.76</v>
+        <v>-490386745.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>124714896.97</v>
+        <v>-151185204.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>-837024157.03</v>
+        <v>-925319974.84</v>
       </c>
       <c r="AD2" t="n">
-        <v>240596084.39</v>
+        <v>-132602668.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-532423312.09</v>
+        <v>718721101.84</v>
       </c>
       <c r="AF2" t="n">
-        <v>1163960441.2</v>
+        <v>973223825.6799999</v>
       </c>
       <c r="AG2" t="n">
-        <v>5517724035.36</v>
+        <v>2683819201.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>69400893.33</v>
+        <v>72283750.34999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>5448323142.03</v>
+        <v>2611535451.09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-64308824.37</v>
+        <v>-54581332.98</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1310386191.2</v>
+        <v>-921423382</v>
       </c>
       <c r="AL2" t="n">
-        <v>70033165.08</v>
+        <v>130780978.94</v>
       </c>
       <c r="AM2" t="n">
-        <v>4485544570.97</v>
+        <v>2131620293.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>-523583026.25</v>
+        <v>-846283778.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-12181906848.89</v>
+        <v>-31296323684.57</v>
       </c>
       <c r="AP2" t="n">
-        <v>-5380436139.82</v>
+        <v>-21663608905.84</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-5368744333.03</v>
+        <v>-6440428499.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1432726376.04</v>
+        <v>-3192286278.93</v>
       </c>
       <c r="AS2" t="n">
-        <v>17191034446.11</v>
+        <v>34274227756.12</v>
       </c>
       <c r="AT2" t="n">
-        <v>4699715102.51</v>
+        <v>20295773614.72</v>
       </c>
       <c r="AU2" t="n">
-        <v>12491319343.6</v>
+        <v>13978454141.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>4389172847.49</v>
+        <v>4005126480.85</v>
       </c>
       <c r="C3" t="n">
-        <v>-2439923132.81</v>
+        <v>-2943928200</v>
       </c>
       <c r="D3" t="n">
-        <v>2261127786.08</v>
+        <v>2624723104.67</v>
       </c>
       <c r="E3" t="n">
-        <v>-284299756.72</v>
+        <v>-306355341.25</v>
       </c>
       <c r="F3" t="n">
-        <v>3274586769.68</v>
+        <v>3419924208.43</v>
       </c>
       <c r="G3" t="n">
-        <v>3419924208.43</v>
+        <v>3621870848.38</v>
       </c>
       <c r="H3" t="n">
-        <v>181857.97</v>
+        <v>786159.0699999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-145519296.72</v>
+        <v>-202732799.02</v>
       </c>
       <c r="J3" t="n">
-        <v>-13196277233.67</v>
+        <v>-11127833178.37</v>
       </c>
       <c r="K3" t="n">
-        <v>-12858467683.03</v>
+        <v>-10609112329.49</v>
       </c>
       <c r="L3" t="n">
-        <v>-146596776.16</v>
+        <v>-184142590.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-178795346.73</v>
+        <v>-319205095.33</v>
       </c>
       <c r="N3" t="n">
-        <v>-178795346.73</v>
+        <v>-319205095.33</v>
       </c>
       <c r="O3" t="n">
-        <v>-2439923132.81</v>
+        <v>-2943928200</v>
       </c>
       <c r="P3" t="n">
-        <v>2261127786.08</v>
+        <v>2624723104.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>8377285332.74</v>
+        <v>6613618557.25</v>
       </c>
       <c r="R3" t="n">
-        <v>8848383.58</v>
+        <v>19663006.88</v>
       </c>
       <c r="S3" t="n">
-        <v>1525148383.58</v>
+        <v>2709060046.99</v>
       </c>
       <c r="T3" t="n">
-        <v>-1516300000</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+        <v>-2689397040.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5045274.08</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5045274.08</v>
+      </c>
       <c r="W3" t="n">
-        <v>8368436949.16</v>
+        <v>6588910276.29</v>
       </c>
       <c r="X3" t="n">
-        <v>8652736705.879999</v>
+        <v>6895265617.54</v>
       </c>
       <c r="Y3" t="n">
-        <v>-284299756.72</v>
+        <v>-306355341.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>4673472604.21</v>
+        <v>4311481822.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-124474104.96</v>
+        <v>-509168822.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>-84746453.84999999</v>
+        <v>-100415175.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>-553285408.59</v>
+        <v>-930534420.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>48157160.57</v>
+        <v>110753743.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>465400596.91</v>
+        <v>411027030.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>1205391642.55</v>
+        <v>1266454360.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>5124084997.68</v>
+        <v>4854159997.55</v>
       </c>
       <c r="AH3" t="n">
-        <v>46815441.91</v>
+        <v>53585615.82</v>
       </c>
       <c r="AI3" t="n">
-        <v>5077269555.77</v>
+        <v>4800574381.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>43580015.19</v>
+        <v>-14834421.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1206159872.14</v>
+        <v>-1088738726.01</v>
       </c>
       <c r="AL3" t="n">
-        <v>-849964211.64</v>
+        <v>-335525764.21</v>
       </c>
       <c r="AM3" t="n">
-        <v>4673472604.21</v>
+        <v>4311481822.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>-665780446.3200001</v>
+        <v>-673533458.89</v>
       </c>
       <c r="AO3" t="n">
-        <v>-13041709197.81</v>
+        <v>-18106010385.78</v>
       </c>
       <c r="AP3" t="n">
-        <v>-5605235650.16</v>
+        <v>-10459799751.66</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-5232540234.01</v>
+        <v>-4828485294.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2203933313.64</v>
+        <v>-2817725339.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>18380962248.34</v>
+        <v>23091025666.77</v>
       </c>
       <c r="AT3" t="n">
-        <v>5399268942.29</v>
+        <v>10756698712.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>12981693306.05</v>
+        <v>12334326954.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>4005126480.85</v>
+        <v>4389172847.49</v>
       </c>
       <c r="C4" t="n">
-        <v>-2943928200</v>
+        <v>-2439923132.81</v>
       </c>
       <c r="D4" t="n">
-        <v>2624723104.67</v>
+        <v>2261127786.08</v>
       </c>
       <c r="E4" t="n">
-        <v>-306355341.25</v>
+        <v>-284299756.72</v>
       </c>
       <c r="F4" t="n">
+        <v>3274586769.68</v>
+      </c>
+      <c r="G4" t="n">
         <v>3419924208.43</v>
       </c>
-      <c r="G4" t="n">
-        <v>3621870848.38</v>
-      </c>
       <c r="H4" t="n">
-        <v>786159.0699999999</v>
+        <v>181857.97</v>
       </c>
       <c r="I4" t="n">
-        <v>-202732799.02</v>
+        <v>-145519296.72</v>
       </c>
       <c r="J4" t="n">
-        <v>-11127833178.37</v>
+        <v>-13196277233.67</v>
       </c>
       <c r="K4" t="n">
-        <v>-10609112329.49</v>
+        <v>-12858467683.03</v>
       </c>
       <c r="L4" t="n">
-        <v>-184142590.61</v>
+        <v>-146596776.16</v>
       </c>
       <c r="M4" t="n">
-        <v>-319205095.33</v>
+        <v>-178795346.73</v>
       </c>
       <c r="N4" t="n">
-        <v>-319205095.33</v>
+        <v>-178795346.73</v>
       </c>
       <c r="O4" t="n">
-        <v>-2943928200</v>
+        <v>-2439923132.81</v>
       </c>
       <c r="P4" t="n">
-        <v>2624723104.67</v>
+        <v>2261127786.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6613618557.25</v>
+        <v>8377285332.74</v>
       </c>
       <c r="R4" t="n">
-        <v>19663006.88</v>
+        <v>8848383.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2709060046.99</v>
+        <v>1525148383.58</v>
       </c>
       <c r="T4" t="n">
-        <v>-2689397040.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5045274.08</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5045274.08</v>
-      </c>
+        <v>-1516300000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>6588910276.29</v>
+        <v>8368436949.16</v>
       </c>
       <c r="X4" t="n">
-        <v>6895265617.54</v>
+        <v>8652736705.879999</v>
       </c>
       <c r="Y4" t="n">
-        <v>-306355341.25</v>
+        <v>-284299756.72</v>
       </c>
       <c r="Z4" t="n">
-        <v>4311481822.1</v>
+        <v>4673472604.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>-509168822.6</v>
+        <v>-124474104.96</v>
       </c>
       <c r="AB4" t="n">
-        <v>-100415175.85</v>
+        <v>-84746453.84999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-930534420.3</v>
+        <v>-553285408.59</v>
       </c>
       <c r="AD4" t="n">
-        <v>110753743.2</v>
+        <v>48157160.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>411027030.35</v>
+        <v>465400596.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>1266454360.44</v>
+        <v>1205391642.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>4854159997.55</v>
+        <v>5124084997.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>53585615.82</v>
+        <v>46815441.91</v>
       </c>
       <c r="AI4" t="n">
-        <v>4800574381.73</v>
+        <v>5077269555.77</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-14834421.29</v>
+        <v>43580015.19</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1088738726.01</v>
+        <v>-1206159872.14</v>
       </c>
       <c r="AL4" t="n">
-        <v>-335525764.21</v>
+        <v>-849964211.64</v>
       </c>
       <c r="AM4" t="n">
-        <v>4311481822.1</v>
+        <v>4673472604.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>-673533458.89</v>
+        <v>-665780446.3200001</v>
       </c>
       <c r="AO4" t="n">
-        <v>-18106010385.78</v>
+        <v>-13041709197.81</v>
       </c>
       <c r="AP4" t="n">
-        <v>-10459799751.66</v>
+        <v>-5605235650.16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-4828485294.38</v>
+        <v>-5232540234.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2817725339.74</v>
+        <v>-2203933313.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>23091025666.77</v>
+        <v>18380962248.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>10756698712.57</v>
+        <v>5399268942.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>12334326954.2</v>
+        <v>12981693306.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1299076970.68</v>
+        <v>4099379863.63</v>
       </c>
       <c r="C5" t="n">
-        <v>-2885498675.68</v>
+        <v>-1991848866.89</v>
       </c>
       <c r="D5" t="n">
-        <v>3124976372.33</v>
+        <v>1716075709.62</v>
       </c>
       <c r="E5" t="n">
-        <v>-832543322.5700001</v>
+        <v>-386164707.34</v>
       </c>
       <c r="F5" t="n">
-        <v>3621870848.38</v>
+        <v>2900006155.94</v>
       </c>
       <c r="G5" t="n">
-        <v>3766128713.76</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-266417.55</v>
-      </c>
+        <v>3274586769.68</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>-143991447.83</v>
+        <v>-374580613.74</v>
       </c>
       <c r="J5" t="n">
-        <v>-4631513518.2</v>
+        <v>-13682324675.41</v>
       </c>
       <c r="K5" t="n">
-        <v>-4632691858.56</v>
+        <v>-13281215338.76</v>
       </c>
       <c r="L5" t="n">
-        <v>-224854653.72</v>
+        <v>-118476179.38</v>
       </c>
       <c r="M5" t="n">
-        <v>239477696.65</v>
+        <v>-275773157.27</v>
       </c>
       <c r="N5" t="n">
-        <v>239477696.65</v>
+        <v>-275773157.27</v>
       </c>
       <c r="O5" t="n">
-        <v>-2885498675.68</v>
+        <v>-1991848866.89</v>
       </c>
       <c r="P5" t="n">
-        <v>3124976372.33</v>
+        <v>1716075709.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2355901777.12</v>
+        <v>8822199490.700001</v>
       </c>
       <c r="R5" t="n">
-        <v>-284597915.56</v>
+        <v>14021037.09</v>
       </c>
       <c r="S5" t="n">
-        <v>4877467888.84</v>
+        <v>1045021037.09</v>
       </c>
       <c r="T5" t="n">
-        <v>-5162065804.4</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+        <v>-1031000000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>169906567.9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>169906567.9</v>
+      </c>
       <c r="W5" t="n">
-        <v>2640499692.68</v>
+        <v>8638271885.709999</v>
       </c>
       <c r="X5" t="n">
-        <v>3473043015.25</v>
+        <v>9024436593.049999</v>
       </c>
       <c r="Y5" t="n">
-        <v>-832543322.5700001</v>
+        <v>-386164707.34</v>
       </c>
       <c r="Z5" t="n">
-        <v>2131620293.25</v>
+        <v>4485544570.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>-490386745.67</v>
+        <v>-1004136487.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>-151185204.17</v>
+        <v>124714896.97</v>
       </c>
       <c r="AC5" t="n">
-        <v>-925319974.84</v>
+        <v>-837024157.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>-132602668.5</v>
+        <v>240596084.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>718721101.84</v>
+        <v>-532423312.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>973223825.6799999</v>
+        <v>1163960441.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>2683819201.44</v>
+        <v>5517724035.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>72283750.34999999</v>
+        <v>69400893.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>2611535451.09</v>
+        <v>5448323142.03</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-54581332.98</v>
+        <v>-64308824.37</v>
       </c>
       <c r="AK5" t="n">
-        <v>-921423382</v>
+        <v>-1310386191.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>130780978.94</v>
+        <v>70033165.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>2131620293.25</v>
+        <v>4485544570.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>-846283778.3</v>
+        <v>-523583026.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>-31296323684.57</v>
+        <v>-12181906848.89</v>
       </c>
       <c r="AP5" t="n">
-        <v>-21663608905.84</v>
+        <v>-5380436139.82</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-6440428499.8</v>
+        <v>-5368744333.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3192286278.93</v>
+        <v>-1432726376.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>34274227756.12</v>
+        <v>17191034446.11</v>
       </c>
       <c r="AT5" t="n">
-        <v>20295773614.72</v>
+        <v>4699715102.51</v>
       </c>
       <c r="AU5" t="n">
-        <v>13978454141.4</v>
+        <v>12491319343.6</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EV2"/>
+  <dimension ref="A1:ET2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3690,600 +3690,590 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>targetHighPrice</t>
-        </is>
-      </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>targetLowPrice</t>
+          <t>recommendationMean</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>targetMeanPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>targetMedianPrice</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>earningsTimestampEnd</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
         <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
       <c r="ER1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverageChangePercent</t>
+          <t>sourceInterval</t>
         </is>
       </c>
       <c r="ES1" t="inlineStr">
         <is>
-          <t>sourceInterval</t>
+          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="ET1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4365,7 +4355,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Yong  Xie', 'age': 53, 'title': 'President &amp; Chairman of the board', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Haiqiong  Zhang', 'age': 53, 'title': 'Financial Director &amp; Accounting Supervisor', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wen Juan  Dai', 'age': 44, 'title': 'VP, GM of Audit Department &amp; Director', 'yearBorn': 1981, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tianlong  Zou', 'age': 41, 'title': 'Board Secretary &amp; Non-Independent Director', 'yearBorn': 1984, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaohui  Gao', 'age': 46, 'title': 'Vice President', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yang  Liu', 'age': 48, 'title': 'Vice President', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mang  Duan', 'age': 55, 'title': 'Vice President', 'yearBorn': 1970, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4380,34 +4370,34 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="V2" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AD2" t="n">
         <v>1751500800</v>
@@ -4419,409 +4409,405 @@
         <v>0.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>25.272728</v>
+        <v>0.622</v>
       </c>
       <c r="AH2" t="n">
-        <v>144236241</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>144236241</v>
+        <v>74364587</v>
       </c>
       <c r="AJ2" t="n">
-        <v>114120243</v>
+        <v>74364587</v>
       </c>
       <c r="AK2" t="n">
-        <v>97182948</v>
+        <v>94201039</v>
       </c>
       <c r="AL2" t="n">
-        <v>97182948</v>
+        <v>68175301</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.78</v>
+        <v>68175301</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6548292096</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>6548292365</v>
+        <v>5182102016</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.73</v>
+        <v>5182101872</v>
       </c>
       <c r="AT2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU2" t="n">
         <v>3.65</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>14.960442</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>0.470676</v>
       </c>
-      <c r="AW2" t="n">
-        <v>0.66698503</v>
-      </c>
       <c r="AX2" t="n">
-        <v>2.9574</v>
+        <v>0.52782995</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.04995</v>
+        <v>2.8222</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>3.00765</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="BC2" t="b">
+      <c r="BD2" t="b">
         <v>0</v>
       </c>
-      <c r="BD2" t="n">
-        <v>13351914496</v>
-      </c>
       <c r="BE2" t="n">
+        <v>11945517056</v>
+      </c>
+      <c r="BF2" t="n">
         <v>-0.00993</v>
       </c>
-      <c r="BF2" t="n">
-        <v>1689594673</v>
-      </c>
       <c r="BG2" t="n">
+        <v>1679283667</v>
+      </c>
+      <c r="BH2" t="n">
         <v>2355500851</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>0.22288999</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>0.15833001</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>2355500851</v>
       </c>
-      <c r="BK2" t="n">
-        <v>3.916</v>
-      </c>
       <c r="BL2" t="n">
-        <v>0.70990807</v>
+        <v>3.94</v>
       </c>
       <c r="BM2" t="n">
+        <v>0.5583756600000001</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>-0.131</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>-97450808</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BS2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="BT2" t="n">
         <v>0.11</v>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>1.3:1</t>
         </is>
       </c>
-      <c r="BU2" t="n">
+      <c r="BV2" t="n">
         <v>1530057600</v>
       </c>
-      <c r="BV2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BW2" t="n">
-        <v>-20.539</v>
+        <v>1.217</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.09150326</v>
+        <v>-18.367</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27697718</v>
+        <v>-0.24398625</v>
       </c>
       <c r="BZ2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="CA2" t="n">
         <v>0.0043</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CB2" t="n">
         <v>1751500800</v>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="CC2" t="n">
-        <v>2.78</v>
-      </c>
       <c r="CD2" t="n">
-        <v>3.16</v>
+        <v>2.2</v>
       </c>
       <c r="CE2" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>3.16</v>
+        <v>1</v>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
       </c>
       <c r="CG2" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
+        <v>3109227776</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.32</v>
       </c>
       <c r="CI2" t="n">
-        <v>1</v>
+        <v>-650379968</v>
       </c>
       <c r="CJ2" t="n">
-        <v>3109227776</v>
+        <v>9826830336</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.312</v>
+        <v>0.618</v>
       </c>
       <c r="CL2" t="n">
-        <v>-650071104</v>
+        <v>0.764</v>
       </c>
       <c r="CM2" t="n">
-        <v>9826830336</v>
+        <v>9817749504</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.387</v>
+        <v>105.356</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.764</v>
+        <v>4.145</v>
       </c>
       <c r="CP2" t="n">
-        <v>9817749504</v>
+        <v>-0.01695</v>
       </c>
       <c r="CQ2" t="n">
-        <v>105.356</v>
+        <v>-0.010249999</v>
       </c>
       <c r="CR2" t="n">
-        <v>4.145</v>
+        <v>931123968</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.01695</v>
+        <v>3410576128</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0.010249999</v>
+        <v>2622963712</v>
       </c>
       <c r="CU2" t="n">
-        <v>931123968</v>
+        <v>-0.148</v>
       </c>
       <c r="CV2" t="n">
-        <v>3364861184</v>
+        <v>-0.234</v>
       </c>
       <c r="CW2" t="n">
-        <v>2622963712</v>
+        <v>0.094840005</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0.148</v>
+        <v>-0.06625</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.234</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.094840005</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>-0.06621</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.044060003</v>
+        <v>-0.0465</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>000560.SZ</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>000560.SZ</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.26853186</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1651492800</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DL2" t="n">
         <v>0</v>
       </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>5I5J HOLDING GROUP CO LTD</t>
-        </is>
-      </c>
       <c r="DM2" t="n">
-        <v>1.090908</v>
+        <v>2.2</v>
       </c>
       <c r="DN2" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>5i5j Holding Group Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
+          <t>2.1 - 2.21</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>94201039</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.10000014</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.04761912</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>2.1 - 3.65</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.39726028</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-24.398624</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>1.0 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.6222</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.2204663</v>
+      </c>
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="EB2" t="n">
         <v>760152600000</v>
       </c>
-      <c r="DR2" t="n">
-        <v>0.029999971</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>2.75 - 2.9</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>114120243</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.049999952</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.018315</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>2.73 - 3.65</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.8700001000000001</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.23835619</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-9.150326</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1651229940</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1651492800</v>
-      </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EE2" t="n">
-        <v>1780038252</v>
+      <c r="ED2" t="n">
+        <v>1782111888</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>SHZ</t>
+          <t>finmb_12726148</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>finmb_12726148</t>
+          <t>Asia/Shanghai</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="EJ2" t="n">
+      <c r="EI2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
       </c>
       <c r="EL2" t="b">
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0.04</v>
+        <v>1651229940</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.17740011</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.059985157</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.2699499</v>
+        <v>-0.80764985</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>5I5J HOLDING GROUP CO LTD</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>5i5j Holding Group Co., Ltd.</t>
+        </is>
       </c>
       <c r="ER2" t="n">
-        <v>-0.08850962</v>
+        <v>15</v>
       </c>
       <c r="ES2" t="n">
         <v>15</v>
       </c>
-      <c r="ET2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EV2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
